--- a/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,87 +421,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ngay_cong_bo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>linh_vuc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>loai_hinh</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>trang_thai_xep_hang</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>loai_y_kien</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ky_han</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ket_qua_xep_hang</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>trien_vong</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ma_trai_phieu</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bao_cao_vi</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>bao_cao_en</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>link_to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>issuer_id</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>to_chuc_xhtn</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>thoi_gian_scrape</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ngay_cong_bo_dt</t>
         </is>
@@ -573,10 +561,10 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="n">
         <v>46203</v>
       </c>
     </row>
@@ -634,10 +622,10 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -695,10 +683,10 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="n">
         <v>46202</v>
       </c>
     </row>
@@ -760,10 +748,10 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="n">
         <v>46198</v>
       </c>
     </row>
@@ -821,10 +809,10 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="n">
         <v>46185</v>
       </c>
     </row>
@@ -882,10 +870,10 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q7" s="1" t="n">
         <v>46169</v>
       </c>
     </row>
@@ -947,10 +935,10 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="n">
         <v>46127</v>
       </c>
     </row>
@@ -1008,10 +996,10 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q9" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -1069,10 +1057,10 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>46016</v>
       </c>
     </row>
@@ -1130,10 +1118,10 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="n">
         <v>46016</v>
       </c>
     </row>
@@ -1191,10 +1179,10 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:38:08</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="n">
+          <t>2026-09-18 07:51:22</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="n">
         <v>45965</v>
       </c>
     </row>

--- a/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:22</t>
+          <t>2026-09-18 08:13:36</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">

--- a/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:36</t>
+          <t>2026-09-18 08:21:26</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">

--- a/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:26</t>
+          <t>2026-09-18 08:50:00</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">

--- a/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:50:00</t>
+          <t>2026-09-18 09:05:40</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">

--- a/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:40</t>
+          <t>2026-09-18 09:22:49</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">

--- a/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260918.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:49</t>
+          <t>2026-09-18 13:07:00</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
